--- a/data/trans_orig/P33B5_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P33B5_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que toma algún remedio para dormir (no medicamentos) en 2023</t>
+          <t>Población según la frecuencia con la que toma algún remedio para dormir (no medicamentos) en 2023 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16776</t>
+          <t>17493</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36024</t>
+          <t>36057</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20960</t>
+          <t>21998</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39215</t>
+          <t>39238</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43081</t>
+          <t>42215</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68835</t>
+          <t>67789</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,12%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7414</t>
+          <t>7620</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19749</t>
+          <t>19978</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6810</t>
+          <t>6838</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17964</t>
+          <t>18913</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16542</t>
+          <t>15727</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33692</t>
+          <t>32461</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21508</t>
+          <t>21746</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40926</t>
+          <t>41748</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25549</t>
+          <t>25562</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43044</t>
+          <t>42918</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>50879</t>
+          <t>52197</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>77543</t>
+          <t>77364</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>421482</t>
+          <t>422178</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>450471</t>
+          <t>449877</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>360725</t>
+          <t>360190</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>385017</t>
+          <t>385070</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>792156</t>
+          <t>790705</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>829633</t>
+          <t>830174</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>87,14%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13931</t>
+          <t>14773</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30732</t>
+          <t>31935</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12937</t>
+          <t>12783</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25753</t>
+          <t>26355</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>30591</t>
+          <t>30286</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>53990</t>
+          <t>50461</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4571</t>
+          <t>4647</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15386</t>
+          <t>15922</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4346</t>
+          <t>4154</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13025</t>
+          <t>13307</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10731</t>
+          <t>10575</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24129</t>
+          <t>24697</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21014</t>
+          <t>20696</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41175</t>
+          <t>41470</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>20997</t>
+          <t>21638</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37173</t>
+          <t>37509</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47796</t>
+          <t>47430</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>74541</t>
+          <t>73020</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>377341</t>
+          <t>375742</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>403786</t>
+          <t>403625</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>314978</t>
+          <t>315498</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>337250</t>
+          <t>337554</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>700124</t>
+          <t>699397</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>734410</t>
+          <t>734462</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10000</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>48595</t>
+          <t>49801</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15412</t>
+          <t>14945</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>29040</t>
+          <t>28448</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>21010</t>
+          <t>20039</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>74344</t>
+          <t>73705</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1621</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14641</t>
+          <t>14896</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>1338</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8574</t>
+          <t>8694</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3447</t>
+          <t>3542</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>19930</t>
+          <t>18957</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8619</t>
+          <t>9507</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>44746</t>
+          <t>46975</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>10121</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21036</t>
+          <t>21679</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17918</t>
+          <t>19253</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61340</t>
+          <t>63441</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>566966</t>
+          <t>563249</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>646370</t>
+          <t>643326</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>117992</t>
+          <t>118845</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>134539</t>
+          <t>136645</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>71,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>687002</t>
+          <t>685656</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>790395</t>
+          <t>789432</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,52%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48537</t>
+          <t>47871</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80401</t>
+          <t>79684</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25130</t>
+          <t>24135</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>69219</t>
+          <t>67982</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>76653</t>
+          <t>79010</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>135829</t>
+          <t>134444</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11706</t>
+          <t>11510</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>26844</t>
+          <t>25832</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9769</t>
+          <t>9441</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29376</t>
+          <t>29005</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>26037</t>
+          <t>24130</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>50768</t>
+          <t>48650</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>62939</t>
+          <t>64744</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>96264</t>
+          <t>98633</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>28424</t>
+          <t>28683</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>75314</t>
+          <t>75908</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>93787</t>
+          <t>89913</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>162677</t>
+          <t>163690</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>850721</t>
+          <t>848679</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>896371</t>
+          <t>896703</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>809823</t>
+          <t>810803</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>909963</t>
+          <t>909572</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1678673</t>
+          <t>1683543</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1812550</t>
+          <t>1821883</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,54%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12403</t>
+          <t>12571</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27439</t>
+          <t>27313</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>68841</t>
+          <t>70360</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>114696</t>
+          <t>117925</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>90464</t>
+          <t>91158</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>134512</t>
+          <t>135506</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,33%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>14487</t>
+          <t>15418</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>29079</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>51827</t>
+          <t>54452</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>37438</t>
+          <t>37679</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>61440</t>
+          <t>61343</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22813</t>
+          <t>21776</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>47646</t>
+          <t>46814</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>56072</t>
+          <t>59115</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>94826</t>
+          <t>96783</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>89110</t>
+          <t>87977</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>132714</t>
+          <t>130181</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>397078</t>
+          <t>397930</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>426797</t>
+          <t>426764</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>593147</t>
+          <t>590225</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>678768</t>
+          <t>678787</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,7 +3395,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1006852</t>
+          <t>1005976</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1085447</t>
+          <t>1089587</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>76,67%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>83,05%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>732</t>
+          <t>677</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6706</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>74139</t>
+          <t>72817</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>100704</t>
+          <t>101135</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>75809</t>
+          <t>75460</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>103800</t>
+          <t>105615</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>21349</t>
+          <t>19567</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>29424</t>
+          <t>28835</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>46480</t>
+          <t>46412</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>32205</t>
+          <t>31262</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>56523</t>
+          <t>55589</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>1445</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>16491</t>
+          <t>14102</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>67612</t>
+          <t>68281</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>95293</t>
+          <t>95286</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>72086</t>
+          <t>71885</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>102463</t>
+          <t>103924</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>213051</t>
+          <t>213211</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>235429</t>
+          <t>234997</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>537077</t>
+          <t>535444</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>577435</t>
+          <t>575469</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,47 +3964,47 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,33%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
+          <t>75,58%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>885</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>785475</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>759833</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>808878</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>78,4%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
           <t>75,84%</t>
         </is>
       </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>885</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>785475</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>761759</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>809740</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>78,4%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>76,03%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>80,74%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>122307</t>
+          <t>121217</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>184320</t>
+          <t>187347</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>245760</t>
+          <t>245033</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>334905</t>
+          <t>338043</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>397095</t>
+          <t>391903</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>508220</t>
+          <t>505861</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>43238</t>
+          <t>42872</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>76437</t>
+          <t>75417</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>96101</t>
+          <t>97522</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>139252</t>
+          <t>142293</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>154949</t>
+          <t>148539</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>208352</t>
+          <t>205040</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>153688</t>
+          <t>155519</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>235415</t>
+          <t>236110</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>240038</t>
+          <t>239279</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>327032</t>
+          <t>327806</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>429100</t>
+          <t>431900</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>548907</t>
+          <t>545932</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2905448</t>
+          <t>2903901</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3049253</t>
+          <t>3051905</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2794378</t>
+          <t>2792812</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2993722</t>
+          <t>3000085</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>5720481</t>
+          <t>5724582</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5965542</t>
+          <t>5965556</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">

--- a/data/trans_orig/P33B5_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P33B5_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>24950</t>
+          <t>26445</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17493</t>
+          <t>17555</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36057</t>
+          <t>36526</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>29284</t>
+          <t>33414</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21998</t>
+          <t>24301</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39238</t>
+          <t>43973</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>54234</t>
+          <t>59859</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42215</t>
+          <t>47179</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>67789</t>
+          <t>76213</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12542</t>
+          <t>13151</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7620</t>
+          <t>7746</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19978</t>
+          <t>21162</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11134</t>
+          <t>12832</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6838</t>
+          <t>7533</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18913</t>
+          <t>20398</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>23676</t>
+          <t>25984</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15727</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>32461</t>
+          <t>35160</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30381</t>
+          <t>32765</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21746</t>
+          <t>23536</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41748</t>
+          <t>45716</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>33509</t>
+          <t>36425</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25562</t>
+          <t>28721</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42918</t>
+          <t>46219</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>63890</t>
+          <t>69190</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>52197</t>
+          <t>57683</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>77364</t>
+          <t>86159</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>437340</t>
+          <t>478256</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>422178</t>
+          <t>462114</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>449877</t>
+          <t>492639</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>373539</t>
+          <t>405740</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>360190</t>
+          <t>392145</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>385070</t>
+          <t>418784</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>810879</t>
+          <t>883996</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>790705</t>
+          <t>864400</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>830174</t>
+          <t>904976</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,1%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21706</t>
+          <t>22898</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14773</t>
+          <t>15053</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>31935</t>
+          <t>32921</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18676</t>
+          <t>22838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12783</t>
+          <t>15980</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26355</t>
+          <t>31382</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>40382</t>
+          <t>45736</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>30286</t>
+          <t>35302</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>50461</t>
+          <t>59182</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4647</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15922</t>
+          <t>16470</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>8623</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4154</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13307</t>
+          <t>14608</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>16504</t>
+          <t>17736</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10575</t>
+          <t>11830</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24697</t>
+          <t>26292</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,9%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>30762</t>
+          <t>33974</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20696</t>
+          <t>24208</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41470</t>
+          <t>45761</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28638</t>
+          <t>31415</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21638</t>
+          <t>23393</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>37509</t>
+          <t>40876</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>59400</t>
+          <t>65389</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47430</t>
+          <t>52946</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73020</t>
+          <t>80571</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>390976</t>
+          <t>417226</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>375742</t>
+          <t>403826</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>403625</t>
+          <t>432072</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>326941</t>
+          <t>359598</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>315498</t>
+          <t>347951</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>337554</t>
+          <t>371650</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>717917</t>
+          <t>776824</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>699397</t>
+          <t>756333</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>734462</t>
+          <t>794602</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>87,73%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>381990</t>
+          <t>422474</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>381990</t>
+          <t>422474</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>381990</t>
+          <t>422474</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>834203</t>
+          <t>905686</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>834203</t>
+          <t>905686</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>834203</t>
+          <t>905686</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>27961</t>
+          <t>30121</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8545</t>
+          <t>22559</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49801</t>
+          <t>42231</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>20940</t>
+          <t>23106</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14945</t>
+          <t>16581</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28448</t>
+          <t>31181</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>48902</t>
+          <t>53227</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20039</t>
+          <t>42904</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>73705</t>
+          <t>67740</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7066</t>
+          <t>7340</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>3695</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14896</t>
+          <t>13399</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4116</t>
+          <t>4619</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1929</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8694</t>
+          <t>9603</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>11182</t>
+          <t>11959</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3542</t>
+          <t>6662</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>18957</t>
+          <t>18318</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>26379</t>
+          <t>28051</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9507</t>
+          <t>19962</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46975</t>
+          <t>39958</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14929</t>
+          <t>15920</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10121</t>
+          <t>11184</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21679</t>
+          <t>22413</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>41308</t>
+          <t>43971</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19253</t>
+          <t>33355</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63441</t>
+          <t>55800</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,47%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>606858</t>
+          <t>406099</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>563249</t>
+          <t>390767</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>643326</t>
+          <t>418912</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,81%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>126926</t>
+          <t>143853</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>118845</t>
+          <t>134190</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>136645</t>
+          <t>152628</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>76,04%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,2%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>733784</t>
+          <t>549952</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>685656</t>
+          <t>533155</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>789432</t>
+          <t>565281</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>80,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>85,76%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>61630</t>
+          <t>68068</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47871</t>
+          <t>55146</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79684</t>
+          <t>88385</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>50508</t>
+          <t>55971</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24135</t>
+          <t>44854</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>67982</t>
+          <t>68671</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>112138</t>
+          <t>124039</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79010</t>
+          <t>104941</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>134444</t>
+          <t>146023</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>7,33%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>17712</t>
+          <t>20243</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11510</t>
+          <t>13469</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>25832</t>
+          <t>31057</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>20010</t>
+          <t>22549</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9441</t>
+          <t>16188</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>29005</t>
+          <t>30727</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>37722</t>
+          <t>42792</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24130</t>
+          <t>33082</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>48650</t>
+          <t>55841</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>79329</t>
+          <t>87748</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>64744</t>
+          <t>70114</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>98633</t>
+          <t>104799</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>56620</t>
+          <t>61685</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>28683</t>
+          <t>50406</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>75908</t>
+          <t>74057</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>135949</t>
+          <t>149433</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>89913</t>
+          <t>129231</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>163690</t>
+          <t>170425</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>876149</t>
+          <t>955784</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>848679</t>
+          <t>930437</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>896703</t>
+          <t>979677</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>850389</t>
+          <t>720410</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>810803</t>
+          <t>703596</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>909572</t>
+          <t>736732</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1726538</t>
+          <t>1676194</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1683543</t>
+          <t>1649484</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1821883</t>
+          <t>1709760</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>82,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>85,81%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>18523</t>
+          <t>21003</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12571</t>
+          <t>13727</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27313</t>
+          <t>30024</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>94001</t>
+          <t>98840</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>70360</t>
+          <t>85252</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>117925</t>
+          <t>115081</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>112523</t>
+          <t>119842</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>91158</t>
+          <t>104183</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>135506</t>
+          <t>138796</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>8732</t>
+          <t>9640</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15418</t>
+          <t>16860</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>40937</t>
+          <t>46987</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>36942</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>54452</t>
+          <t>58749</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>49669</t>
+          <t>56627</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>37679</t>
+          <t>46084</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>61343</t>
+          <t>70475</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>32041</t>
+          <t>36045</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21776</t>
+          <t>25361</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>46814</t>
+          <t>48994</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>77706</t>
+          <t>88744</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>59115</t>
+          <t>75324</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>96783</t>
+          <t>105480</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>109747</t>
+          <t>124790</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>87977</t>
+          <t>107082</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>130181</t>
+          <t>145878</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>413723</t>
+          <t>499206</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>397930</t>
+          <t>483569</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>426764</t>
+          <t>513815</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>626352</t>
+          <t>595556</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>590225</t>
+          <t>573143</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>678787</t>
+          <t>614855</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>71,74%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>70,35%</t>
+          <t>69,04%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1040075</t>
+          <t>1094762</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1005976</t>
+          <t>1066540</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1089587</t>
+          <t>1120678</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>80,28%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>473019</t>
+          <t>565894</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>473019</t>
+          <t>565894</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>473019</t>
+          <t>565894</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>838996</t>
+          <t>830127</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1312015</t>
+          <t>1396022</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1312015</t>
+          <t>1396022</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1312015</t>
+          <t>1396022</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3570,17 +3570,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>2548</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>706</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>6802</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>86388</t>
+          <t>94164</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>72817</t>
+          <t>79272</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>101135</t>
+          <t>110133</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>88965</t>
+          <t>96712</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>75460</t>
+          <t>83172</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>105615</t>
+          <t>116045</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,73%</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3683,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>3906</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>19567</t>
+          <t>18226</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>37007</t>
+          <t>42061</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>28835</t>
+          <t>33127</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>46412</t>
+          <t>52176</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>41362</t>
+          <t>45967</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>31262</t>
+          <t>35743</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>55589</t>
+          <t>60919</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>5380</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>14102</t>
+          <t>14290</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>80696</t>
+          <t>87178</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>68281</t>
+          <t>73708</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>95286</t>
+          <t>105185</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>86076</t>
+          <t>92671</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>71885</t>
+          <t>78629</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>103924</t>
+          <t>109998</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>228196</t>
+          <t>225280</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>213211</t>
+          <t>211279</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>234997</t>
+          <t>232151</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>557280</t>
+          <t>620878</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>535444</t>
+          <t>596708</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>575469</t>
+          <t>642705</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,54%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>785475</t>
+          <t>846158</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>759833</t>
+          <t>818623</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>808878</t>
+          <t>868636</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>78,4%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>80,32%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1001878</t>
+          <t>1081509</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>157346</t>
+          <t>171083</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>121217</t>
+          <t>149442</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>187347</t>
+          <t>198243</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>299797</t>
+          <t>328333</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>245033</t>
+          <t>300891</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>338043</t>
+          <t>357145</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>457143</t>
+          <t>499416</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>391903</t>
+          <t>463857</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>505861</t>
+          <t>538415</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,61%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>59175</t>
+          <t>63395</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>42872</t>
+          <t>49917</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>75417</t>
+          <t>81494</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>120940</t>
+          <t>137670</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>97522</t>
+          <t>119767</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>142293</t>
+          <t>157562</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>180115</t>
+          <t>201066</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>148539</t>
+          <t>178319</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>205040</t>
+          <t>225824</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>204272</t>
+          <t>224077</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>155519</t>
+          <t>194697</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>236110</t>
+          <t>253668</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>292099</t>
+          <t>321368</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>239279</t>
+          <t>293436</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>327806</t>
+          <t>349566</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>496370</t>
+          <t>545445</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>431900</t>
+          <t>508833</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>545932</t>
+          <t>592459</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,38%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2953241</t>
+          <t>2981851</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2903901</t>
+          <t>2941644</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>3051905</t>
+          <t>3021404</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>2861428</t>
+          <t>2846035</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>2792812</t>
+          <t>2804244</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>3000085</t>
+          <t>2888260</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>78,33%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>79,49%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>5814668</t>
+          <t>5827886</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>5724582</t>
+          <t>5760954</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>5965556</t>
+          <t>5885713</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>83,2%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3374034</t>
+          <t>3440407</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3374034</t>
+          <t>3440407</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3374034</t>
+          <t>3440407</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3574263</t>
+          <t>3633406</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3574263</t>
+          <t>3633406</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3574263</t>
+          <t>3633406</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>6948297</t>
+          <t>7073812</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6948297</t>
+          <t>7073812</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6948297</t>
+          <t>7073812</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
